--- a/data/trans_camb/P74B-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P74B-Provincia-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8,85; 31,69</t>
+          <t>8,17; 31,83</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,44; 18,66</t>
+          <t>0,18; 19,34</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-37,99; -9,12</t>
+          <t>-37,0; -6,38</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-59,73; -28,3</t>
+          <t>-57,26; -26,76</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,63; 25,64</t>
+          <t>2,79; 25,66</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-12,62; 8,58</t>
+          <t>-11,62; 9,68</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>62,1; 681,46</t>
+          <t>58,86; 696,92</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,94; 366,3</t>
+          <t>-5,9; 395,85</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-39,77; -10,48</t>
+          <t>-39,07; -7,75</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-63,65; -33,6</t>
+          <t>-61,04; -31,73</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,93; 103,48</t>
+          <t>7,77; 108,27</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-35,17; 34,26</t>
+          <t>-32,25; 38,78</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 8,22</t>
+          <t>-1,41; 8,7</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 5,16</t>
+          <t>-2,76; 5,56</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-20,8; 1,49</t>
+          <t>-20,75; 1,97</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-26,05; -2,85</t>
+          <t>-25,18; -3,08</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 13,57</t>
+          <t>-0,24; 13,26</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,57; 8,98</t>
+          <t>-3,6; 9,59</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-24,27; 295,64</t>
+          <t>-25,03; 303,5</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-42,52; 176,46</t>
+          <t>-43,59; 224,14</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-25,09; 2,05</t>
+          <t>-24,71; 2,73</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-30,99; -3,46</t>
+          <t>-30,48; -4,37</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 61,18</t>
+          <t>-0,65; 60,96</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-12,01; 40,06</t>
+          <t>-12,29; 44,82</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,18; 12,19</t>
+          <t>0,93; 12,45</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,48; 15,7</t>
+          <t>3,64; 16,77</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-29,85; 0,17</t>
+          <t>-29,97; -0,86</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-35,68; -7,34</t>
+          <t>-34,55; -4,57</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-6,36; 12,03</t>
+          <t>-5,72; 11,96</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 13,73</t>
+          <t>-4,05; 13,21</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 834,5</t>
+          <t>-7,68; 733,38</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>24,74; 1149,44</t>
+          <t>35,28; 937,13</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-34,37; -0,3</t>
+          <t>-33,24; -1,18</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-40,67; -10,08</t>
+          <t>-39,43; -6,44</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-20,81; 55,7</t>
+          <t>-19,52; 50,86</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-11,16; 61,38</t>
+          <t>-14,0; 58,38</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 16,64</t>
+          <t>-2,2; 17,15</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,82; 12,2</t>
+          <t>-4,94; 11,11</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-16,72; 7,27</t>
+          <t>-16,5; 6,62</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-26,36; -1,19</t>
+          <t>-25,12; -0,75</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 16,69</t>
+          <t>-0,75; 18,41</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-5,14; 12,38</t>
+          <t>-4,57; 12,94</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-12,6; 174,04</t>
+          <t>-14,92; 171,4</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-23,82; 131,98</t>
+          <t>-27,6; 116,09</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-19,19; 9,44</t>
+          <t>-18,73; 8,72</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-29,57; -1,5</t>
+          <t>-28,45; -1,07</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-3,95; 51,8</t>
+          <t>-3,08; 55,98</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-12,05; 38,78</t>
+          <t>-10,92; 41,04</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-6,96; 16,58</t>
+          <t>-6,54; 15,66</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,05; 23,29</t>
+          <t>0,17; 22,82</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-33,14; 1,41</t>
+          <t>-32,84; -0,49</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-36,81; -3,64</t>
+          <t>-38,1; -5,03</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-12,02; 11,14</t>
+          <t>-12,12; 12,23</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-9,91; 12,57</t>
+          <t>-10,44; 12,14</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-43,03; 262,73</t>
+          <t>-43,31; 262,97</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 369,24</t>
+          <t>-4,33; 338,6</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-36,63; 1,79</t>
+          <t>-36,69; -1,27</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-41,71; -6,9</t>
+          <t>-42,14; -7,15</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-27,2; 34,49</t>
+          <t>-27,06; 38,37</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-22,01; 39,6</t>
+          <t>-23,33; 37,82</t>
         </is>
       </c>
     </row>
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>1,39; 13,31</t>
+          <t>1,2; 12,56</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 6,84</t>
+          <t>-3,19; 7,51</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-39,45; -11,54</t>
+          <t>-40,32; -10,93</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-26,85; 1,53</t>
+          <t>-27,01; 2,41</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-6,55; 10,72</t>
+          <t>-6,45; 11,24</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-4,97; 14,77</t>
+          <t>-5,7; 14,9</t>
         </is>
       </c>
     </row>
@@ -1487,32 +1487,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-5,33; 1245,5</t>
+          <t>0,48; 1181,69</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-82,54; 671,18</t>
+          <t>-100,0; 811,44</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-45,76; -15,89</t>
+          <t>-45,5; -14,0</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-31,55; 1,87</t>
+          <t>-30,56; 3,23</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-20,01; 44,95</t>
+          <t>-20,89; 48,2</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-15,32; 63,68</t>
+          <t>-17,34; 66,5</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 10,4</t>
+          <t>-0,51; 10,29</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-3,91; 6,63</t>
+          <t>-3,52; 6,9</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-25,0; -4,32</t>
+          <t>-24,92; -4,11</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-25,64; -1,61</t>
+          <t>-24,85; -2,7</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 11,17</t>
+          <t>-2,57; 10,76</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-6,7; 7,52</t>
+          <t>-5,95; 7,54</t>
         </is>
       </c>
     </row>
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-13,45; 164,94</t>
+          <t>-6,28; 165,01</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-37,5; 111,8</t>
+          <t>-36,14; 111,81</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-29,2; -6,06</t>
+          <t>-28,99; -5,44</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-30,06; -2,13</t>
+          <t>-28,83; -3,54</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-7,78; 41,91</t>
+          <t>-7,32; 39,31</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-19,82; 27,41</t>
+          <t>-18,15; 27,38</t>
         </is>
       </c>
     </row>
@@ -1723,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-4,73; 4,76</t>
+          <t>-4,04; 5,3</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>1,09; 11,75</t>
+          <t>1,64; 12,04</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-23,97; -5,43</t>
+          <t>-23,7; -5,7</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-20,33; -1,41</t>
+          <t>-20,94; -2,19</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-5,08; 7,4</t>
+          <t>-4,42; 7,42</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 12,63</t>
+          <t>0,4; 12,64</t>
         </is>
       </c>
     </row>
@@ -1799,32 +1799,32 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-45,07; 77,05</t>
+          <t>-38,65; 86,78</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>7,24; 175,83</t>
+          <t>10,57; 180,3</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-27,73; -7,35</t>
+          <t>-27,52; -7,44</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-23,53; -1,97</t>
+          <t>-23,88; -2,85</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-14,83; 26,92</t>
+          <t>-13,07; 26,94</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 46,16</t>
+          <t>1,13; 45,75</t>
         </is>
       </c>
     </row>
@@ -1879,32 +1879,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>2,54; 7,45</t>
+          <t>2,67; 7,2</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>2,71; 7,22</t>
+          <t>2,51; 7,31</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-19,0; -10,59</t>
+          <t>-18,68; -10,18</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-21,3; -12,08</t>
+          <t>-21,04; -12,02</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>1,78; 7,47</t>
+          <t>1,65; 7,39</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0,51; 6,24</t>
+          <t>0,42; 6,33</t>
         </is>
       </c>
     </row>
@@ -1955,32 +1955,32 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>28,74; 115,32</t>
+          <t>30,2; 109,08</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>31,16; 111,49</t>
+          <t>31,15; 110,36</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-22,32; -12,99</t>
+          <t>-22,16; -12,55</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-25,17; -14,89</t>
+          <t>-24,97; -14,84</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>5,59; 25,72</t>
+          <t>5,23; 25,55</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>1,58; 21,55</t>
+          <t>1,4; 21,78</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P74B-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P74B-Provincia-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8,17; 31,83</t>
+          <t>7,75; 31,8</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,18; 19,34</t>
+          <t>-0,4; 18,76</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-37,0; -6,38</t>
+          <t>-37,96; -7,65</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-57,26; -26,76</t>
+          <t>-58,41; -27,04</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,79; 25,66</t>
+          <t>3,1; 26,51</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-11,62; 9,68</t>
+          <t>-12,53; 8,91</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>58,86; 696,92</t>
+          <t>50,27; 653,28</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,9; 395,85</t>
+          <t>-11,06; 367,27</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-39,07; -7,75</t>
+          <t>-39,78; -8,97</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-61,04; -31,73</t>
+          <t>-61,6; -32,35</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,77; 108,27</t>
+          <t>7,75; 104,23</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-32,25; 38,78</t>
+          <t>-34,82; 36,82</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 8,7</t>
+          <t>-1,1; 9,72</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 5,56</t>
+          <t>-3,41; 4,8</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-20,75; 1,97</t>
+          <t>-20,73; 1,97</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-25,18; -3,08</t>
+          <t>-25,76; -1,86</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 13,26</t>
+          <t>0,53; 14,02</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 9,59</t>
+          <t>-3,08; 10,21</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-25,03; 303,5</t>
+          <t>-20,98; 318,89</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-43,59; 224,14</t>
+          <t>-52,19; 156,02</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-24,71; 2,73</t>
+          <t>-25,45; 2,06</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-30,48; -4,37</t>
+          <t>-31,02; -3,01</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 60,96</t>
+          <t>1,66; 64,59</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-12,29; 44,82</t>
+          <t>-10,87; 47,49</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,93; 12,45</t>
+          <t>0,66; 11,85</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,64; 16,77</t>
+          <t>3,3; 15,64</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-29,97; -0,86</t>
+          <t>-30,07; 0,74</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-34,55; -4,57</t>
+          <t>-33,97; -6,62</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,72; 11,96</t>
+          <t>-5,94; 11,61</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 13,21</t>
+          <t>-4,06; 13,1</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-7,68; 733,38</t>
+          <t>-6,23; 775,9</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>35,28; 937,13</t>
+          <t>41,19; 1058,5</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-33,24; -1,18</t>
+          <t>-33,33; 1,1</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-39,43; -6,44</t>
+          <t>-38,58; -8,92</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-19,52; 50,86</t>
+          <t>-20,66; 52,97</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-14,0; 58,38</t>
+          <t>-13,68; 58,91</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 17,15</t>
+          <t>-2,36; 16,32</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,94; 11,11</t>
+          <t>-4,56; 11,11</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-16,5; 6,62</t>
+          <t>-15,5; 7,52</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-25,12; -0,75</t>
+          <t>-25,05; -0,32</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 18,41</t>
+          <t>-0,44; 18,31</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,57; 12,94</t>
+          <t>-4,56; 12,95</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-14,92; 171,4</t>
+          <t>-15,32; 160,43</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-27,6; 116,09</t>
+          <t>-27,37; 113,26</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-18,73; 8,72</t>
+          <t>-17,78; 9,76</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-28,45; -1,07</t>
+          <t>-28,65; -1,32</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 55,98</t>
+          <t>-0,13; 58,69</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-10,92; 41,04</t>
+          <t>-11,72; 40,57</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-6,54; 15,66</t>
+          <t>-7,03; 16,05</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,17; 22,82</t>
+          <t>1,02; 23,21</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-32,84; -0,49</t>
+          <t>-32,5; -0,66</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-38,1; -5,03</t>
+          <t>-37,66; -6,97</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-12,12; 12,23</t>
+          <t>-12,18; 11,87</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-10,44; 12,14</t>
+          <t>-10,51; 12,09</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-43,31; 262,97</t>
+          <t>-47,7; 226,21</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-4,33; 338,6</t>
+          <t>-0,78; 362,12</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-36,69; -1,27</t>
+          <t>-36,16; -1,47</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-42,14; -7,15</t>
+          <t>-42,56; -10,91</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-27,06; 38,37</t>
+          <t>-27,41; 37,57</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-23,33; 37,82</t>
+          <t>-23,49; 37,63</t>
         </is>
       </c>
     </row>
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>1,2; 12,56</t>
+          <t>1,34; 12,55</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 7,51</t>
+          <t>-2,88; 6,9</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-40,32; -10,93</t>
+          <t>-39,53; -10,52</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-27,01; 2,41</t>
+          <t>-26,4; 2,55</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-6,45; 11,24</t>
+          <t>-7,09; 11,63</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-5,7; 14,9</t>
+          <t>-4,5; 15,12</t>
         </is>
       </c>
     </row>
@@ -1487,32 +1487,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0,48; 1181,69</t>
+          <t>2,25; 1154,73</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 811,44</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-45,5; -14,0</t>
+          <t>-45,51; -14,79</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-30,56; 3,23</t>
+          <t>-30,44; 3,1</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-20,89; 48,2</t>
+          <t>-21,71; 49,97</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-17,34; 66,5</t>
+          <t>-14,33; 68,46</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 10,29</t>
+          <t>-0,54; 10,46</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 6,9</t>
+          <t>-4,29; 6,81</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-24,92; -4,11</t>
+          <t>-23,45; -2,96</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-24,85; -2,7</t>
+          <t>-24,7; -2,37</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 10,76</t>
+          <t>-3,0; 10,34</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-5,95; 7,54</t>
+          <t>-5,99; 8,2</t>
         </is>
       </c>
     </row>
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-6,28; 165,01</t>
+          <t>-6,01; 182,52</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-36,14; 111,81</t>
+          <t>-41,47; 113,05</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-28,99; -5,44</t>
+          <t>-27,93; -4,12</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-28,83; -3,54</t>
+          <t>-28,79; -3,27</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-7,32; 39,31</t>
+          <t>-8,68; 39,02</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-18,15; 27,38</t>
+          <t>-18,03; 30,32</t>
         </is>
       </c>
     </row>
@@ -1723,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 5,3</t>
+          <t>-3,72; 5,28</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>1,64; 12,04</t>
+          <t>1,07; 11,94</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-23,7; -5,7</t>
+          <t>-24,68; -6,08</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-20,94; -2,19</t>
+          <t>-21,38; -1,43</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-4,42; 7,42</t>
+          <t>-5,26; 6,96</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,4; 12,64</t>
+          <t>-0,39; 12,41</t>
         </is>
       </c>
     </row>
@@ -1799,32 +1799,32 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-38,65; 86,78</t>
+          <t>-36,42; 88,46</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>10,57; 180,3</t>
+          <t>7,79; 189,05</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-27,52; -7,44</t>
+          <t>-28,14; -7,78</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-23,88; -2,85</t>
+          <t>-24,63; -2,09</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-13,07; 26,94</t>
+          <t>-15,09; 25,14</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>1,13; 45,75</t>
+          <t>-1,04; 44,38</t>
         </is>
       </c>
     </row>
@@ -1879,32 +1879,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>2,67; 7,2</t>
+          <t>2,53; 7,36</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>2,51; 7,31</t>
+          <t>2,71; 7,44</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-18,68; -10,18</t>
+          <t>-19,22; -10,15</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-21,04; -12,02</t>
+          <t>-21,07; -11,76</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>1,65; 7,39</t>
+          <t>1,59; 7,31</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0,42; 6,33</t>
+          <t>0,49; 6,06</t>
         </is>
       </c>
     </row>
@@ -1955,32 +1955,32 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>30,2; 109,08</t>
+          <t>29,53; 110,76</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>31,15; 110,36</t>
+          <t>30,53; 111,31</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-22,16; -12,55</t>
+          <t>-22,67; -12,58</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-24,97; -14,84</t>
+          <t>-24,95; -14,62</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>5,23; 25,55</t>
+          <t>4,97; 25,24</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>1,4; 21,78</t>
+          <t>1,68; 21,29</t>
         </is>
       </c>
     </row>
